--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/model_metrics.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/model_metrics.xlsx
@@ -477,20 +477,20 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.225</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3083333333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1868589743589744</v>
+        <v>0.3474556489262371</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1757936507936508</v>
+        <v>0.3266051895815961</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -509,17 +509,17 @@
         <v>0.4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1994047619047619</v>
+        <v>0.2352430555555556</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2392344497607655</v>
+        <v>0.2398989898989899</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2132978723404255</v>
+        <v>0.224969474969475</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -535,20 +535,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.275</v>
+        <v>0.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3587962962962963</v>
+        <v>0.126984126984127</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2731481481481481</v>
+        <v>0.159469696969697</v>
       </c>
       <c r="F4" t="n">
-        <v>0.273015873015873</v>
+        <v>0.1410457516339869</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -564,20 +564,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.55</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1239495798319328</v>
+        <v>0.3048780487804878</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1488095238095238</v>
+        <v>0.1918367346938775</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1320197044334976</v>
+        <v>0.1902392797915186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -593,20 +593,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.275</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1794871794871795</v>
+        <v>0.3068322981366459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2033333333333333</v>
+        <v>0.307449494949495</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1870945479641132</v>
+        <v>0.3011586239847109</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -622,20 +622,20 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.75</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="D7" t="n">
-        <v>0.25</v>
+        <v>0.4761904761904761</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4184704184704184</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4177777777777778</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -651,20 +651,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4652777777777778</v>
+        <v>0.6117948717948718</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3661764705882353</v>
+        <v>0.4682860998650473</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3753958065896448</v>
+        <v>0.5106837606837608</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -680,20 +680,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.4</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1529017857142857</v>
+        <v>0.217948717948718</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1978021978021978</v>
+        <v>0.26875</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1665094339622641</v>
+        <v>0.2291666666666667</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -709,16 +709,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.45</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.184375</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3092105263157894</v>
+        <v>0.2340909090909091</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3024010872848082</v>
+        <v>0.2046296296296296</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -738,20 +738,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.4</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1669565217391304</v>
+        <v>0.1740740740740741</v>
       </c>
       <c r="E11" t="n">
-        <v>0.219047619047619</v>
+        <v>0.2109803921568628</v>
       </c>
       <c r="F11" t="n">
-        <v>0.188021778584392</v>
+        <v>0.1874608150470219</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -767,20 +767,20 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.375</v>
+        <v>0.3111111111111111</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3408333333333333</v>
+        <v>0.19</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3137529137529137</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3180901856763926</v>
+        <v>0.2077777777777778</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -796,20 +796,20 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1614035087719298</v>
+        <v>0.1615384615384615</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2125</v>
+        <v>0.1941176470588235</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1828571428571429</v>
+        <v>0.1731601731601732</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 2, 'min_samples_split': 5, 'n_estimators': 200}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.075</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02704678362573099</v>
+        <v>0.0616421568627451</v>
       </c>
       <c r="E14" t="n">
-        <v>0.040625</v>
+        <v>0.07803030303030303</v>
       </c>
       <c r="F14" t="n">
-        <v>0.031947261663286</v>
+        <v>0.06623931623931624</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -854,20 +854,20 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.325</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3083333333333333</v>
+        <v>0.1852747678018576</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2853535353535354</v>
+        <v>0.2191558441558442</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2841269841269841</v>
+        <v>0.198847558779647</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -883,20 +883,20 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.375</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="D16" t="n">
-        <v>0.32</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="E16" t="n">
-        <v>0.31007326007326</v>
+        <v>0.4633766233766233</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3071561771561772</v>
+        <v>0.4949826814276942</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -912,20 +912,20 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.725</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2478632478632479</v>
+        <v>0.9224806201550387</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2843137254901961</v>
+        <v>0.4799498746867168</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -941,20 +941,20 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.5</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="D18" t="n">
-        <v>0.32</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3472222222222222</v>
+        <v>0.4012204424103737</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3319308087891538</v>
+        <v>0.3832778394376619</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -970,20 +970,20 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.525</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3046594982078853</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="E19" t="n">
-        <v>0.327536231884058</v>
+        <v>0.3256172839506173</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3055555555555555</v>
+        <v>0.292929292929293</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -999,20 +999,20 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.375</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3538961038961039</v>
+        <v>0.3154411764705882</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3652777777777778</v>
+        <v>0.3277972027972028</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3566742081447963</v>
+        <v>0.3170426065162907</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1028,20 +1028,20 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.45</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3155929038281979</v>
+        <v>0.6266339869281046</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3627450980392157</v>
+        <v>0.5411793372319688</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3370547581073897</v>
+        <v>0.5582010582010583</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1057,20 +1057,20 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.4</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3756720430107527</v>
+        <v>0.2869318181818182</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2967320261437909</v>
+        <v>0.2879186602870814</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2869734432234432</v>
+        <v>0.2772576260948354</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.3</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2715508021390375</v>
+        <v>0.2536363636363636</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2627272727272727</v>
+        <v>0.253030303030303</v>
       </c>
       <c r="F23" t="n">
-        <v>0.261692789968652</v>
+        <v>0.2326984126984127</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1115,20 +1115,20 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.225</v>
+        <v>0.2</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1821052631578947</v>
+        <v>0.1378280542986425</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1938888888888889</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1776709678706049</v>
+        <v>0.1499550224887556</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1144,20 +1144,20 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.3</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5210526315789473</v>
+        <v>0.4976851851851852</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.4272486772486772</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2957393483709273</v>
+        <v>0.4240949334816669</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 2, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -1173,20 +1173,20 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.75</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="D26" t="n">
-        <v>0.375</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4155844155844156</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 200}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1202,20 +1202,20 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.425</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2714285714285715</v>
+        <v>0.2786458333333333</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2643387314439946</v>
+        <v>0.2780032467532467</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2484126984126984</v>
+        <v>0.2642914653784219</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -1231,20 +1231,20 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.35</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="D28" t="n">
-        <v>0.189327485380117</v>
+        <v>0.4594298245614035</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.3090277777777778</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2090017825311943</v>
+        <v>0.3045366795366795</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1260,20 +1260,20 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2843137254901961</v>
+        <v>0.2115987460815047</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2740183792815372</v>
+        <v>0.2702020202020202</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2426100628930818</v>
+        <v>0.2372549019607843</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -1289,20 +1289,20 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.675</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3981481481481481</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="E30" t="n">
-        <v>0.382716049382716</v>
+        <v>0.3247311827956989</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3671143671143671</v>
+        <v>0.3089814087457449</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 2, 'min_samples_split': 5, 'n_estimators': 100}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1318,20 +1318,20 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2735042735042735</v>
+        <v>0.6136363636363636</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3232323232323233</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.3997648442092887</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1347,20 +1347,20 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.85</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.2740740740740741</v>
       </c>
       <c r="E32" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3063063063063063</v>
+        <v>0.3008130081300813</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.4</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2123563218390805</v>
+        <v>0.2145833333333333</v>
       </c>
       <c r="E33" t="n">
-        <v>0.23125</v>
+        <v>0.2532608695652174</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2119047619047619</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1405,20 +1405,20 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.325</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2957393483709273</v>
+        <v>0.431002331002331</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3091491841491842</v>
+        <v>0.424074074074074</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2994708994708994</v>
+        <v>0.4242424242424243</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 200}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1434,20 +1434,20 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D35" t="n">
-        <v>0.265993265993266</v>
+        <v>0.2326086956521739</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3223039215686275</v>
+        <v>0.2705882352941176</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2911010558069382</v>
+        <v>0.2501571338780641</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1466,17 +1466,17 @@
         <v>0.4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3618181818181818</v>
+        <v>0.1750663129973475</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2982142857142857</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3108287961282516</v>
+        <v>0.1848862802641233</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'entropy', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -1492,20 +1492,20 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.575</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2017543859649123</v>
+        <v>0.2850877192982456</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3066666666666667</v>
+        <v>0.3209876543209877</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2433862433862434</v>
+        <v>0.2871794871794872</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1521,20 +1521,20 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.6</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="D38" t="n">
-        <v>0.375</v>
+        <v>0.4532520325203253</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3924191750278707</v>
+        <v>0.3919413919413919</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3694083694083694</v>
+        <v>0.3598673300165838</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1550,20 +1550,20 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.35</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1505376344086022</v>
+        <v>0.3098039215686275</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3452380952380952</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1794871794871795</v>
+        <v>0.3180076628352491</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1579,20 +1579,20 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.5</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3295238095238096</v>
+        <v>0.7129987129987129</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3650793650793651</v>
+        <v>0.4361111111111111</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3457556935817805</v>
+        <v>0.4459584131715279</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -1608,20 +1608,20 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4718045112781955</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4340659340659341</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4301994301994302</v>
+        <v>0.4585561497326204</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 100}</t>
+          <t>{'criterion': 'entropy', 'max_depth': 10, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 100}</t>
         </is>
       </c>
     </row>
@@ -1637,20 +1637,20 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.425</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2711111111111111</v>
+        <v>0.2407407407407407</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2798573975044563</v>
+        <v>0.247719298245614</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2743794326241135</v>
+        <v>0.2439362439362439</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>{'criterion': 'gini', 'max_depth': None, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'criterion': 'gini', 'max_depth': 10, 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
